--- a/copy/COPYS_FASE1_AWARENESS.xlsx
+++ b/copy/COPYS_FASE1_AWARENESS.xlsx
@@ -49,7 +49,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000A6B63"/>
+      <color rgb="001F4E79"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -62,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A6B63"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
